--- a/output/pdf_financials_xlsx/ECO.xlsx
+++ b/output/pdf_financials_xlsx/ECO.xlsx
@@ -510,11 +510,15 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0.926884</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>1.108646</v>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
@@ -1025,10 +1029,10 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0</v>
+        <v>0.926884</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0</v>
+        <v>1.108646</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
@@ -1524,10 +1528,10 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-2.530758</v>
+        <v>-3.457642</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>-1.454058</v>
+        <v>-2.562704</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>-2.402094</v>
@@ -1586,10 +1590,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-1.281812</v>
+        <v>-2.208696</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-0.07299700000000001</v>
+        <v>-1.181643</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>-0.9625899999999999</v>
@@ -1617,10 +1621,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-5.622147914967146</v>
+        <v>-9.687548260740481</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-0.3957137131061756</v>
+        <v>-6.405637753550429</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>-7.045380671522658</v>
@@ -1982,45 +1986,29 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>14.207342</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>7.975713</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>16.637161</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>42.226816</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>4.808606</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>4.915445</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>7.721403</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>8.420285</v>
       </c>
     </row>
     <row r="47">
@@ -2071,38 +2059,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>30.6354</v>
+        <v>44.842742</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>35.720548</v>
+        <v>43.696261</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>25.344575</v>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>41.981736</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>42.226816</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>4.808606</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>4.915445</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>7.721403</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>8.420285</v>
       </c>
     </row>
     <row r="49">
@@ -2581,10 +2559,10 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>14.476582</v>
+        <v>0.26924</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>8.166642</v>
+        <v>0.190929</v>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
@@ -2592,13 +2570,13 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>42.325422</v>
+        <v>0.098606</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>25.948549</v>
+        <v>21.139943</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>33.374127</v>
+        <v>28.458682</v>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
@@ -6197,7 +6175,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -16507,7 +16485,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">

--- a/output/pdf_financials_xlsx/ECO.xlsx
+++ b/output/pdf_financials_xlsx/ECO.xlsx
@@ -5275,10 +5275,10 @@
         <v>0</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>0</v>
+        <v>0.511038</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I127" s="3" t="n">
         <v>0</v>
@@ -9005,7 +9005,11 @@
           <t>Proceeds on disposal of property, plant and equipment (note 8)</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ECO.xlsx
+++ b/output/pdf_financials_xlsx/ECO.xlsx
@@ -2234,25 +2234,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F52" s="3" t="n">
+        <v>0.301794</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0.114651</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0.070052</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0.011501</v>
       </c>
     </row>
     <row r="53">
@@ -2274,16 +2266,16 @@
         <v>1.91239</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>2.930386</v>
+        <v>3.23218</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>1.549443</v>
+        <v>1.664094</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>2.325369</v>
+        <v>2.395421</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>3.234911</v>
+        <v>3.246412</v>
       </c>
     </row>
     <row r="54">
@@ -2573,10 +2565,10 @@
         <v>0.098606</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>21.139943</v>
+        <v>20.838149</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>28.458682</v>
+        <v>28.344031</v>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
@@ -3238,45 +3230,29 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>1.306645</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>0.536023</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0.560329</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>0.959601</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1.260993</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0.831463</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>0.72904</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0.7703410000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3379,45 +3355,29 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0.948785</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0.623776</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0.380061</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>1.148099</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1.058527</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0.449594</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0.972001</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>1.179534</v>
       </c>
     </row>
     <row r="80">
